--- a/artfynd/A 573-2022 artfynd.xlsx
+++ b/artfynd/A 573-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 573-2022 artfynd.xlsx
+++ b/artfynd/A 573-2022 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89328108</v>
+        <v>89368157</v>
       </c>
       <c r="B2" t="n">
-        <v>93158</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96554</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,48 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2818</v>
+        <v>210</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>kapslar</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>S Arttjärn, Vrm</t>
+          <t>S Arttjärn(Bv2020_S03), Vrm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>406140.9229956659</v>
+        <v>406142</v>
       </c>
       <c r="R2" t="n">
-        <v>6627217.766873891</v>
+        <v>6627219</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +757,9 @@
           <t>2020-10-19</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-10-19</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,6 +771,19 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Gallrad granskog (ca 60-70 år gammal) i lätt östsluttning med husmossa/lågörter.</t>
+        </is>
+      </c>
+      <c r="AN2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Murken gallringsstubbe av gran, ca 20 cm grov.</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
@@ -783,19 +795,18 @@
           <t>Jenny Andersson</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89368157</v>
+        <v>89328108</v>
       </c>
       <c r="B3" t="n">
-        <v>93235</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96458</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,48 +814,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>210</v>
+        <v>2818</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>kapslar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>S Arttjärn(Bv2020_S03), Vrm</t>
+          <t>S Arttjärn, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>406141.9698708526</v>
+        <v>406141</v>
       </c>
       <c r="R3" t="n">
-        <v>6627219.252045926</v>
+        <v>6627218</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -874,19 +871,9 @@
           <t>2020-10-19</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-10-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -898,19 +885,6 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>Gallrad granskog (ca 60-70 år gammal) i lätt östsluttning med husmossa/lågörter.</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Murken gallringsstubbe av gran, ca 20 cm grov.</t>
-        </is>
-      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
@@ -922,11 +896,7 @@
           <t>Jenny Andersson</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Biogeografisk uppföljning av mossor – eftersök i lämpliga miljöer</t>
-        </is>
-      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
